--- a/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T14:31:58+00:00</t>
+    <t>2024-02-19T14:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T14:41:57+00:00</t>
+    <t>2024-02-20T16:47:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T16:47:04+00:00</t>
+    <t>2024-02-26T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
